--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T12:12:39+00:00</t>
+    <t>2024-11-05T09:00:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:00:17+00:00</t>
+    <t>2024-11-05T09:16:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:16:22+00:00</t>
+    <t>2024-11-05T10:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T10:26:22+00:00</t>
+    <t>2024-11-06T09:40:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T09:40:37+00:00</t>
+    <t>2024-11-07T06:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T06:21:30+00:00</t>
+    <t>2024-11-07T13:12:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T13:12:32+00:00</t>
+    <t>2024-11-07T14:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T14:31:26+00:00</t>
+    <t>2024-11-08T06:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-WorkflowStatus-valueset.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>Property</t>
   </si>
@@ -56,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:16:09+00:00</t>
+    <t>2024-11-12T07:45:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,6 +94,21 @@
   </si>
   <si>
     <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>This ValueSet is work in progress.</t>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://tbd.at/moped-ext-workflow-status</t>
   </si>
 </sst>
 </file>
@@ -350,4 +366,50 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>